--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Engagements'!$A$4:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Engagements'!$A$4:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -619,7 +619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E-311</t>
+          <t>Logistics systems rollout</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E-314</t>
+          <t>Retail pricing review</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E-318</t>
+          <t>Health charity board pack</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -649,7 +649,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E-320</t>
+          <t>Manufacturer process mapping</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -659,7 +659,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R-102</t>
+          <t>Construction firm finance</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -669,7 +669,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R-105</t>
+          <t>Dental group reporting</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -679,7 +679,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R-108</t>
+          <t>Agribusiness CFO support</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -689,7 +689,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R-110</t>
+          <t>Hospitality payroll</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -699,7 +699,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T-207</t>
+          <t>Excel for managers</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -709,7 +709,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T-209</t>
+          <t>Power BI basics</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -1855,20 +1855,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1901,42 +1900,37 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>Description</t>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Billed</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>Billed</t>
+          <t>Contractors</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>Contractors</t>
+          <t>Consultant time cost</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Consultant time cost</t>
+          <t>Contribution</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>Margin %</t>
         </is>
@@ -1950,39 +1944,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E-311</t>
+          <t>Agribusiness CFO support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Systems implementation, logistics client</t>
-        </is>
+          <t>Retainer</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>70</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>210</v>
+        <v>12000</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>36750</v>
+        <v>12000</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>4800</v>
+        <v>4200</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>12600</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <v>19350</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>52.7</v>
+        <v>7800</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1993,39 +1982,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E-314</t>
+          <t>Construction firm finance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pricing review, retail group</t>
-        </is>
+          <t>Retainer</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>58</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>96</v>
+        <v>9500</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>18240</v>
+        <v>9500</v>
       </c>
       <c r="G6" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>5760</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>12480</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>68.40000000000001</v>
+        <v>6020</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>63.4</v>
       </c>
     </row>
     <row r="7">
@@ -2036,39 +2020,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E-318</t>
+          <t>Dental group reporting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Board reporting pack, health not-for-profit</t>
-        </is>
+          <t>Retainer</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>44</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>64</v>
+        <v>6800</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>10560</v>
+        <v>6800</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>10560</v>
+        <v>0</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>0</v>
+        <v>2640</v>
       </c>
       <c r="I7" s="22" t="n">
-        <v>3840</v>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>6720</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>63.6</v>
+        <v>4160</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>61.2</v>
       </c>
     </row>
     <row r="8">
@@ -2079,39 +2058,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E-320</t>
+          <t>Excel for managers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Process mapping, manufacturer</t>
-        </is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>30</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>120</v>
+        <v>8800</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>20400</v>
+        <v>8800</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>24000</v>
+        <v>1500</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>7200</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>11000</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>53.9</v>
+        <v>5500</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>62.5</v>
       </c>
     </row>
     <row r="9">
@@ -2122,39 +2096,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R-102</t>
+          <t>Health charity board pack</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Retainer</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Monthly finance, construction firm</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>64</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>58</v>
+        <v>10560</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>9500</v>
+        <v>10560</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>0</v>
+        <v>3840</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>3480</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>6020</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>63.4</v>
+        <v>6720</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>63.6</v>
       </c>
     </row>
     <row r="10">
@@ -2165,7 +2134,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R-105</t>
+          <t>Hospitality payroll</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2173,31 +2142,26 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Monthly reporting, dental group</t>
-        </is>
+      <c r="D10" s="22" t="n">
+        <v>36</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>44</v>
+        <v>4200</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>6800</v>
+        <v>4200</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>2640</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>4160</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>61.2</v>
+        <v>2040</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>48.6</v>
       </c>
     </row>
     <row r="11">
@@ -2208,39 +2172,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R-108</t>
+          <t>Logistics systems rollout</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Retainer</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CFO support, agribusiness</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>210</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>70</v>
+        <v>36750</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>12000</v>
+        <v>30000</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>12000</v>
+        <v>4800</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>4200</v>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>7800</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>65</v>
+        <v>19350</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>52.7</v>
       </c>
     </row>
     <row r="12">
@@ -2251,39 +2210,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R-110</t>
+          <t>Manufacturer process mapping</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Retainer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Payroll and compliance, hospitality group</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>120</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>36</v>
+        <v>20400</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>4200</v>
+        <v>24000</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>4200</v>
+        <v>2200</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>2160</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>2040</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>48.6</v>
+        <v>11000</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>53.9</v>
       </c>
     </row>
     <row r="13">
@@ -2294,7 +2248,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T-207</t>
+          <t>Power BI basics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2302,31 +2256,26 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Excel for managers (2 days)</t>
-        </is>
+      <c r="D13" s="22" t="n">
+        <v>14</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>30</v>
+        <v>4600</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>8800</v>
+        <v>4600</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>1500</v>
+        <v>840</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>1800</v>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>5500</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>62.5</v>
+        <v>3760</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>81.7</v>
       </c>
     </row>
     <row r="14">
@@ -2337,39 +2286,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T-209</t>
+          <t>Retail pricing review</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Power BI basics (1 day)</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>96</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>14</v>
+        <v>18240</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>0</v>
+        <v>5760</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>840</v>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>3760</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>81.7</v>
+        <v>12480</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2380,39 +2324,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>E-311</t>
+          <t>Agribusiness CFO support</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Systems implementation, logistics client</t>
-        </is>
+          <t>Retainer</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>68</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>180</v>
+        <v>12000</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>31500</v>
+        <v>12000</v>
       </c>
       <c r="G15" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>4200</v>
+        <v>4080</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>10800</v>
-      </c>
-      <c r="J15" s="22" t="n">
-        <v>16500</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>52.4</v>
+        <v>7920</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -2423,39 +2362,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E-314</t>
+          <t>Budgeting workshop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Pricing review, retail group</t>
-        </is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>20</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>60</v>
+        <v>6400</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>11400</v>
+        <v>6400</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>3600</v>
-      </c>
-      <c r="J16" s="22" t="n">
-        <v>7800</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>68.40000000000001</v>
+        <v>4300</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>67.2</v>
       </c>
     </row>
     <row r="17">
@@ -2466,39 +2400,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>E-316</t>
+          <t>Construction firm finance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Cost-to-serve analysis, distributor</t>
-        </is>
+          <t>Retainer</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>56</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>88</v>
+        <v>9500</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>15840</v>
+        <v>9500</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>15840</v>
+        <v>0</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>5280</v>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>10560</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>66.7</v>
+        <v>6140</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2509,39 +2438,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>E-320</t>
+          <t>Dental group reporting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Process mapping, manufacturer</t>
-        </is>
+          <t>Retainer</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>42</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>100</v>
+        <v>6800</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>17000</v>
+        <v>6800</v>
       </c>
       <c r="G18" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>1800</v>
+        <v>2520</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>9200</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>54.1</v>
+        <v>4280</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>62.9</v>
       </c>
     </row>
     <row r="19">
@@ -2552,39 +2476,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R-102</t>
+          <t>Distributor cost-to-serve</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Retainer</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Monthly finance, construction firm</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>88</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>56</v>
+        <v>15840</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>9500</v>
+        <v>15840</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>0</v>
+        <v>5280</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>3360</v>
-      </c>
-      <c r="J19" s="22" t="n">
-        <v>6140</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>64.59999999999999</v>
+        <v>10560</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>66.7</v>
       </c>
     </row>
     <row r="20">
@@ -2595,7 +2514,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R-105</t>
+          <t>Hospitality payroll</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2603,31 +2522,26 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Monthly reporting, dental group</t>
-        </is>
+      <c r="D20" s="22" t="n">
+        <v>34</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>42</v>
+        <v>4200</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>6800</v>
+        <v>4200</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>2520</v>
-      </c>
-      <c r="J20" s="22" t="n">
-        <v>4280</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>62.9</v>
+        <v>2160</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>51.4</v>
       </c>
     </row>
     <row r="21">
@@ -2638,39 +2552,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R-108</t>
+          <t>Logistics systems rollout</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Retainer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CFO support, agribusiness</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>180</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>68</v>
+        <v>31500</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>12000</v>
+        <v>4200</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>4080</v>
-      </c>
-      <c r="J21" s="22" t="n">
-        <v>7920</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>66</v>
+        <v>16500</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>52.4</v>
       </c>
     </row>
     <row r="22">
@@ -2681,39 +2590,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R-110</t>
+          <t>Manufacturer process mapping</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Retainer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Payroll and compliance, hospitality group</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>34</v>
+        <v>17000</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>4200</v>
+        <v>1800</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>2040</v>
-      </c>
-      <c r="J22" s="22" t="n">
-        <v>2160</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>51.4</v>
+        <v>9200</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>54.1</v>
       </c>
     </row>
     <row r="23">
@@ -2724,43 +2628,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T-205</t>
+          <t>Retail pricing review</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Budgeting workshop (1 day)</t>
-        </is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>60</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>20</v>
+        <v>11400</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>900</v>
+        <v>3600</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J23" s="22" t="n">
-        <v>4300</v>
-      </c>
-      <c r="K23" s="8" t="n">
-        <v>67.2</v>
+        <v>7800</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>68.40000000000001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K23"/>
+  <autoFilter ref="A4:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -11,11 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PandL" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Engagements'!$A$4:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Engagements'!$A$4:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -122,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,6 +156,13 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1855,6 +1863,1381 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C149"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>How each number is worked out</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · generated 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Consultant utilisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Billable hours ÷ hours available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr"/>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Billable hours (timesheets)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>742 h</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>648 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Consultants</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Working days</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Hours available (consultants × days × 7.6)</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>1,003.2 h</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>912 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Utilisation</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Revenue per billable hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Revenue ÷ billable hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr"/>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>$131,850</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>$114,640</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Billable hours</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>742 h</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>648 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Revenue per hour</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>$178</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>$177</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Retainers and training are fixed fees, so fewer hours on them raises the hourly figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Cash tied up in work</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Work in progress + unpaid invoices at month end</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr"/>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Work in progress (project time not yet billed)</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>$99,290</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>$77,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Unpaid client invoices</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>$116,800</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>$71,290</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Total tied up</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>$216,090</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>$149,190</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Milestone billing on the logistics and manufacturer projects landed at the end of September, so it moved from unbilled to unpaid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Logistics systems rollout</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr"/>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>210 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>$36,750</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>$-4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>210 h × $60 = $-12,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>$19,350</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>52.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Retail pricing review</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr"/>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>96 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>$18,240</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>96 h × $60 = $-5,760</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>$12,480</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>68.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Health charity board pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr"/>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>64 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>$10,560</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>64 h × $60 = $-3,840</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>$6,720</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturer process mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr"/>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>120 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>$20,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>$-2,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>120 h × $60 = $-7,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>$11,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>53.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Construction firm finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr"/>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Retainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>58 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>$9,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>58 h × $60 = $-3,480</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>$6,020</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>63.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Dental group reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr"/>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>Retainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>44 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>$6,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>44 h × $60 = $-2,640</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>$4,160</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>61.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Agribusiness CFO support</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr"/>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>Retainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B108" s="22" t="inlineStr">
+        <is>
+          <t>70 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>$12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>70 h × $60 = $-4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>$7,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>65.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Hospitality payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr"/>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B119" s="22" t="inlineStr">
+        <is>
+          <t>Retainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>36 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B121" s="22" t="inlineStr">
+        <is>
+          <t>$4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B123" s="22" t="inlineStr">
+        <is>
+          <t>36 h × $60 = $-2,160</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B124" s="22" t="inlineStr">
+        <is>
+          <t>$2,040</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B125" s="22" t="inlineStr">
+        <is>
+          <t>48.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Excel for managers</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr"/>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B131" s="22" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B132" s="22" t="inlineStr">
+        <is>
+          <t>30 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B133" s="22" t="inlineStr">
+        <is>
+          <t>$8,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B134" s="22" t="inlineStr">
+        <is>
+          <t>$-1,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B135" s="22" t="inlineStr">
+        <is>
+          <t>30 h × $60 = $-1,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B136" s="22" t="inlineStr">
+        <is>
+          <t>$5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B137" s="22" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Power BI basics</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>Contribution ÷ revenue for this engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="inlineStr"/>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B143" s="22" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="21" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>14 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B145" s="22" t="inlineStr">
+        <is>
+          <t>$4,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="21" t="inlineStr">
+        <is>
+          <t>Contractors</t>
+        </is>
+      </c>
+      <c r="B146" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="21" t="inlineStr">
+        <is>
+          <t>Consultant time</t>
+        </is>
+      </c>
+      <c r="B147" s="22" t="inlineStr">
+        <is>
+          <t>14 h × $60 = $-840</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="21" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>$3,760</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B149" s="22" t="inlineStr">
+        <is>
+          <t>81.7%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1885,52 +3268,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Billed</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Contractors</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>Consultant time cost</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>Margin %</t>
         </is>
@@ -1952,22 +3335,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="25" t="n">
         <v>12000</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="25" t="n">
         <v>12000</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="25" t="n">
         <v>7800</v>
       </c>
       <c r="J5" s="8" t="n">
@@ -1990,22 +3373,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="25" t="n">
         <v>58</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="25" t="n">
         <v>9500</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="25" t="n">
         <v>9500</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="25" t="n">
         <v>3480</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="25" t="n">
         <v>6020</v>
       </c>
       <c r="J6" s="8" t="n">
@@ -2028,22 +3411,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="25" t="n">
         <v>6800</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="25" t="n">
         <v>6800</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="25" t="n">
         <v>2640</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="25" t="n">
         <v>4160</v>
       </c>
       <c r="J7" s="8" t="n">
@@ -2066,22 +3449,22 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="25" t="n">
         <v>8800</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="25" t="n">
         <v>8800</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="25" t="n">
         <v>1500</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="25" t="n">
         <v>1800</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="25" t="n">
         <v>5500</v>
       </c>
       <c r="J8" s="8" t="n">
@@ -2104,22 +3487,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="25" t="n">
         <v>64</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="25" t="n">
         <v>10560</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="25" t="n">
         <v>10560</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="25" t="n">
         <v>3840</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="25" t="n">
         <v>6720</v>
       </c>
       <c r="J9" s="8" t="n">
@@ -2142,22 +3525,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="25" t="n">
         <v>2160</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="25" t="n">
         <v>2040</v>
       </c>
       <c r="J10" s="8" t="n">
@@ -2180,22 +3563,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="25" t="n">
         <v>210</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="25" t="n">
         <v>36750</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="25" t="n">
         <v>4800</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="25" t="n">
         <v>12600</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="25" t="n">
         <v>19350</v>
       </c>
       <c r="J11" s="8" t="n">
@@ -2218,22 +3601,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="25" t="n">
         <v>20400</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="25" t="n">
         <v>24000</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="25" t="n">
         <v>2200</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="25" t="n">
         <v>7200</v>
       </c>
-      <c r="I12" s="22" t="n">
+      <c r="I12" s="25" t="n">
         <v>11000</v>
       </c>
       <c r="J12" s="8" t="n">
@@ -2256,22 +3639,22 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="25" t="n">
         <v>4600</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="25" t="n">
         <v>4600</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="H13" s="25" t="n">
         <v>840</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="25" t="n">
         <v>3760</v>
       </c>
       <c r="J13" s="8" t="n">
@@ -2294,22 +3677,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="25" t="n">
         <v>18240</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="25" t="n">
         <v>5760</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="25" t="n">
         <v>12480</v>
       </c>
       <c r="J14" s="8" t="n">
@@ -2332,22 +3715,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="25" t="n">
         <v>12000</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="25" t="n">
         <v>12000</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="25" t="n">
         <v>4080</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="25" t="n">
         <v>7920</v>
       </c>
       <c r="J15" s="8" t="n">
@@ -2370,22 +3753,22 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="25" t="n">
         <v>6400</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="25" t="n">
         <v>6400</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="25" t="n">
         <v>900</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="25" t="n">
         <v>4300</v>
       </c>
       <c r="J16" s="8" t="n">
@@ -2408,22 +3791,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="25" t="n">
         <v>56</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="25" t="n">
         <v>9500</v>
       </c>
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="25" t="n">
         <v>9500</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="25" t="n">
         <v>3360</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="25" t="n">
         <v>6140</v>
       </c>
       <c r="J17" s="8" t="n">
@@ -2446,22 +3829,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="25" t="n">
         <v>6800</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="25" t="n">
         <v>6800</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="25" t="n">
         <v>2520</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="25" t="n">
         <v>4280</v>
       </c>
       <c r="J18" s="8" t="n">
@@ -2484,22 +3867,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="25" t="n">
         <v>88</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="25" t="n">
         <v>15840</v>
       </c>
-      <c r="F19" s="22" t="n">
+      <c r="F19" s="25" t="n">
         <v>15840</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="25" t="n">
         <v>5280</v>
       </c>
-      <c r="I19" s="22" t="n">
+      <c r="I19" s="25" t="n">
         <v>10560</v>
       </c>
       <c r="J19" s="8" t="n">
@@ -2522,22 +3905,22 @@
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="E20" s="22" t="n">
+      <c r="E20" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="F20" s="22" t="n">
+      <c r="F20" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="25" t="n">
         <v>2040</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="25" t="n">
         <v>2160</v>
       </c>
       <c r="J20" s="8" t="n">
@@ -2560,22 +3943,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="25" t="n">
         <v>31500</v>
       </c>
-      <c r="F21" s="22" t="n">
+      <c r="F21" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="H21" s="25" t="n">
         <v>10800</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="25" t="n">
         <v>16500</v>
       </c>
       <c r="J21" s="8" t="n">
@@ -2598,22 +3981,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="25" t="n">
         <v>17000</v>
       </c>
-      <c r="F22" s="22" t="n">
+      <c r="F22" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="22" t="n">
+      <c r="G22" s="25" t="n">
         <v>1800</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="25" t="n">
         <v>6000</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="25" t="n">
         <v>9200</v>
       </c>
       <c r="J22" s="8" t="n">
@@ -2636,22 +4019,22 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="25" t="n">
         <v>11400</v>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F23" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="22" t="n">
+      <c r="H23" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="25" t="n">
         <v>7800</v>
       </c>
       <c r="J23" s="8" t="n">
@@ -2664,7 +4047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2699,36 +4082,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>A Brisbane finance and operations consultancy: projects billed on milestones, monthly retainers and training. 6 consultants, 3 management and admin staff.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Reporting month</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>September 2026, compared with August 2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Financial year</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>FY2027: 1 July 2026 to 30 June 2027</t>
         </is>
@@ -2742,48 +4125,48 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>hours worked at each project's rate; billed on milestones (unbilled time = work in progress)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>fixed monthly fee, billed monthly</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>fixed fee, billed on delivery</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Engagements in September</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>10 (every one is in the Excel download and CSV)</t>
         </is>
@@ -2797,48 +4180,48 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Consultants</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>6 on salary: $46,500 a month incl. super</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Engagement costing rate</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>$60/hour for consultant time</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Working days</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>20 in August (Ekka show holiday), 22 in September; 7.6 hours a day</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>25% of profit, provided monthly</t>
         </is>
@@ -2852,36 +4235,36 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Client payments</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>each invoice is paid on its own date; unpaid invoices at month end = debtors</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>paid the following month</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>excluded throughout, for simplicity</t>
         </is>

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -16,7 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PandL'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Engagements'!$A$4:$J$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Engagements'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +545,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -566,6 +570,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -627,11 +638,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Logistics systems rollout</t>
+          <t>Power BI basics</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>52.7</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="10">
@@ -647,21 +658,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Health charity board pack</t>
+          <t>Agribusiness CFO support</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>63.6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manufacturer process mapping</t>
+          <t>Health charity board pack</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>53.9</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="13">
@@ -677,51 +688,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dental group reporting</t>
+          <t>Excel for managers</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>61.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agribusiness CFO support</t>
+          <t>Dental group reporting</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>65</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hospitality payroll</t>
+          <t>Manufacturer process mapping</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>48.6</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Excel for managers</t>
+          <t>Logistics systems rollout</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>62.5</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Power BI basics</t>
+          <t>Hospitality payroll</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>81.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +746,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -768,6 +789,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1186,8 +1214,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1220,6 +1257,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1553,8 +1597,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1587,6 +1640,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1852,8 +1912,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1861,7 +1930,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1885,6 +1954,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2170,7 +2246,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Logistics systems rollout</t>
+          <t>Power BI basics</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2273,7 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2285,7 @@
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>210 h</t>
+          <t>14 h</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2297,7 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>$36,750</t>
+          <t>$4,600</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2309,7 @@
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>$-4,800</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2321,7 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>210 h × $60 = $-12,600</t>
+          <t>14 h × $60 = ($840)</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2333,7 @@
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>$19,350</t>
+          <t>$3,760</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2345,7 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>81.7%</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2427,7 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>96 h × $60 = $-5,760</t>
+          <t>96 h × $60 = ($5,760)</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2458,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Health charity board pack</t>
+          <t>Agribusiness CFO support</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2485,7 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Retainer</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2497,7 @@
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>64 h</t>
+          <t>70 h</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2509,7 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>$10,560</t>
+          <t>$12,000</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2533,7 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>64 h × $60 = $-3,840</t>
+          <t>70 h × $60 = ($4,200)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2545,7 @@
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>$6,720</t>
+          <t>$7,800</t>
         </is>
       </c>
     </row>
@@ -2481,14 +2557,14 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Manufacturer process mapping</t>
+          <t>Health charity board pack</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2603,7 @@
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>120 h</t>
+          <t>64 h</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2615,7 @@
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>$20,400</t>
+          <t>$10,560</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2627,7 @@
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>$-2,200</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2639,7 @@
       </c>
       <c r="B75" s="22" t="inlineStr">
         <is>
-          <t>120 h × $60 = $-7,200</t>
+          <t>64 h × $60 = ($3,840)</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2651,7 @@
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>$11,000</t>
+          <t>$6,720</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2663,7 @@
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2745,7 @@
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>58 h × $60 = $-3,480</t>
+          <t>58 h × $60 = ($3,480)</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2776,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Dental group reporting</t>
+          <t>Excel for managers</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2803,7 @@
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>Retainer</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2815,7 @@
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>44 h</t>
+          <t>30 h</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2827,7 @@
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>$6,800</t>
+          <t>$8,800</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2839,7 @@
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>($1,500)</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2851,7 @@
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>44 h × $60 = $-2,640</t>
+          <t>30 h × $60 = ($1,800)</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2863,7 @@
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>$4,160</t>
+          <t>$5,500</t>
         </is>
       </c>
     </row>
@@ -2799,14 +2875,14 @@
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Agribusiness CFO support</t>
+          <t>Dental group reporting</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2921,7 @@
       </c>
       <c r="B108" s="22" t="inlineStr">
         <is>
-          <t>70 h</t>
+          <t>44 h</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2933,7 @@
       </c>
       <c r="B109" s="22" t="inlineStr">
         <is>
-          <t>$12,000</t>
+          <t>$6,800</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2957,7 @@
       </c>
       <c r="B111" s="22" t="inlineStr">
         <is>
-          <t>70 h × $60 = $-4,200</t>
+          <t>44 h × $60 = ($2,640)</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2969,7 @@
       </c>
       <c r="B112" s="22" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$4,160</t>
         </is>
       </c>
     </row>
@@ -2905,14 +2981,14 @@
       </c>
       <c r="B113" s="22" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Hospitality payroll</t>
+          <t>Manufacturer process mapping</t>
         </is>
       </c>
     </row>
@@ -2939,7 +3015,7 @@
       </c>
       <c r="B119" s="22" t="inlineStr">
         <is>
-          <t>Retainer</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3027,7 @@
       </c>
       <c r="B120" s="22" t="inlineStr">
         <is>
-          <t>36 h</t>
+          <t>120 h</t>
         </is>
       </c>
     </row>
@@ -2963,7 +3039,7 @@
       </c>
       <c r="B121" s="22" t="inlineStr">
         <is>
-          <t>$4,200</t>
+          <t>$20,400</t>
         </is>
       </c>
     </row>
@@ -2975,7 +3051,7 @@
       </c>
       <c r="B122" s="22" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>($2,200)</t>
         </is>
       </c>
     </row>
@@ -2987,7 +3063,7 @@
       </c>
       <c r="B123" s="22" t="inlineStr">
         <is>
-          <t>36 h × $60 = $-2,160</t>
+          <t>120 h × $60 = ($7,200)</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3075,7 @@
       </c>
       <c r="B124" s="22" t="inlineStr">
         <is>
-          <t>$2,040</t>
+          <t>$11,000</t>
         </is>
       </c>
     </row>
@@ -3011,14 +3087,14 @@
       </c>
       <c r="B125" s="22" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Excel for managers</t>
+          <t>Logistics systems rollout</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3121,7 @@
       </c>
       <c r="B131" s="22" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3133,7 @@
       </c>
       <c r="B132" s="22" t="inlineStr">
         <is>
-          <t>30 h</t>
+          <t>210 h</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3145,7 @@
       </c>
       <c r="B133" s="22" t="inlineStr">
         <is>
-          <t>$8,800</t>
+          <t>$36,750</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3157,7 @@
       </c>
       <c r="B134" s="22" t="inlineStr">
         <is>
-          <t>$-1,500</t>
+          <t>($4,800)</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3169,7 @@
       </c>
       <c r="B135" s="22" t="inlineStr">
         <is>
-          <t>30 h × $60 = $-1,800</t>
+          <t>210 h × $60 = ($12,600)</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3181,7 @@
       </c>
       <c r="B136" s="22" t="inlineStr">
         <is>
-          <t>$5,500</t>
+          <t>$19,350</t>
         </is>
       </c>
     </row>
@@ -3117,14 +3193,14 @@
       </c>
       <c r="B137" s="22" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Power BI basics</t>
+          <t>Hospitality payroll</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3227,7 @@
       </c>
       <c r="B143" s="22" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Retainer</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3239,7 @@
       </c>
       <c r="B144" s="22" t="inlineStr">
         <is>
-          <t>14 h</t>
+          <t>36 h</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3251,7 @@
       </c>
       <c r="B145" s="22" t="inlineStr">
         <is>
-          <t>$4,600</t>
+          <t>$4,200</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3275,7 @@
       </c>
       <c r="B147" s="22" t="inlineStr">
         <is>
-          <t>14 h × $60 = $-840</t>
+          <t>36 h × $60 = ($2,160)</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3287,7 @@
       </c>
       <c r="B148" s="22" t="inlineStr">
         <is>
-          <t>$3,760</t>
+          <t>$2,040</t>
         </is>
       </c>
     </row>
@@ -3223,12 +3299,22 @@
       </c>
       <c r="B149" s="22" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3236,7 +3322,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3267,6 +3353,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
         <is>
@@ -4043,7 +4136,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:J23"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4051,7 +4154,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4074,6 +4177,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -4320,6 +4430,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -665,14 +665,14 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Margin on each client engagement, September 2026 work only</t>
+          <t>Gross margin on each client engagement, September 2026 work only</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>September's revenue less contractors and consultant time at $60/hour. Not the whole engagement to date. One 40.0% target for every engagement for now.</t>
+          <t>September's revenue less contractors and consultant time at $60/hour. Before overheads: not profit. Not the whole engagement to date. One 40.0% target for every engagement for now.</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Contribution $</t>
+          <t>Gross margin $</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Consultant salaries (incl. super)</t>
+          <t>Consultant salaries (incl. on-costs)</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
@@ -2111,7 +2111,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($ per hour)</t>
+          <t>Consultant cost rate ($ per hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Consultant time cost</t>
+          <t>Consultant time cost (incl. on-costs)</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -3375,7 +3375,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B42" s="20">
@@ -3386,7 +3386,7 @@
     <row r="43">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B43" s="27">
@@ -3406,7 +3406,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
@@ -3472,7 +3472,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B54" s="20">
@@ -3483,7 +3483,7 @@
     <row r="55">
       <c r="A55" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B55" s="27">
@@ -3503,7 +3503,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B64" s="20" t="n">
@@ -3569,7 +3569,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B66" s="20">
@@ -3580,7 +3580,7 @@
     <row r="67">
       <c r="A67" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B67" s="27">
@@ -3600,7 +3600,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B76" s="20" t="n">
@@ -3666,7 +3666,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B78" s="20">
@@ -3677,7 +3677,7 @@
     <row r="79">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B79" s="27">
@@ -3697,7 +3697,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B88" s="20" t="n">
@@ -3763,7 +3763,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B90" s="20">
@@ -3774,7 +3774,7 @@
     <row r="91">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B91" s="27">
@@ -3794,7 +3794,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B100" s="20" t="n">
@@ -3860,7 +3860,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B102" s="20">
@@ -3871,7 +3871,7 @@
     <row r="103">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B103" s="27">
@@ -3891,7 +3891,7 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B112" s="20" t="n">
@@ -3957,7 +3957,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B114" s="20">
@@ -3968,7 +3968,7 @@
     <row r="115">
       <c r="A115" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B115" s="27">
@@ -3988,7 +3988,7 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B124" s="20" t="n">
@@ -4054,7 +4054,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B126" s="20">
@@ -4065,7 +4065,7 @@
     <row r="127">
       <c r="A127" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B127" s="27">
@@ -4085,7 +4085,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B136" s="20" t="n">
@@ -4151,7 +4151,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B138" s="20">
@@ -4162,7 +4162,7 @@
     <row r="139">
       <c r="A139" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B139" s="27">
@@ -4182,7 +4182,7 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>Contribution ÷ revenue for this engagement</t>
+          <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Consultant cost rate ($/hour)</t>
+          <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B148" s="20" t="n">
@@ -4248,7 +4248,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B150" s="20">
@@ -4259,7 +4259,7 @@
     <row r="151">
       <c r="A151" s="26" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B151" s="27">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>6 on salary: $46,500 a month incl. super</t>
+          <t>6 on salary: $46,500 a month incl. on-costs</t>
         </is>
       </c>
     </row>

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -34,57 +34,69 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="002F7A5D"/>
@@ -131,33 +143,33 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -168,15 +180,15 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -854,8 +866,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Advisory Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 services-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1336,8 +1348,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Advisory Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 services-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1731,8 +1743,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Advisory Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 services-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2056,8 +2068,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Advisory Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 services-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2987,8 +2999,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Advisory Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 services-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4275,8 +4287,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Advisory Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 services-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4638,8 +4650,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Advisory Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 services-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -779,7 +779,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Excel for managers</t>
+          <t>Dental group reporting</t>
         </is>
       </c>
       <c r="B19" s="5">
@@ -794,7 +794,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dental group reporting</t>
+          <t>Manufacturer process mapping</t>
         </is>
       </c>
       <c r="B20" s="5">
@@ -809,7 +809,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manufacturer process mapping</t>
+          <t>Logistics systems rollout</t>
         </is>
       </c>
       <c r="B21" s="5">
@@ -824,7 +824,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Logistics systems rollout</t>
+          <t>Excel for managers</t>
         </is>
       </c>
       <c r="B22" s="5">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>-8500</v>
+        <v>-17600</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>-6900</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>-6178</v>
+        <v>-3903</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>-1898</v>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>8500</v>
+        <v>17600</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>6900</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56576</v>
+        <v>54301</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>50398</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>218574</v>
+        <v>211749</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>200042</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E10" s="20" t="n">
         <v>8800</v>
@@ -2332,7 +2332,7 @@
         <v>8800</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>1500</v>
+        <v>4200</v>
       </c>
       <c r="H10" s="20">
         <f>D10*$B$4</f>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E12" s="20" t="n">
         <v>4200</v>
@@ -2455,7 +2455,7 @@
         <v>30000</v>
       </c>
       <c r="G13" s="20" t="n">
-        <v>4800</v>
+        <v>11200</v>
       </c>
       <c r="H13" s="20">
         <f>D13*$B$4</f>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E22" s="20" t="n">
         <v>4200</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>648</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>648</v>
+        <v>662</v>
       </c>
     </row>
     <row r="21">
@@ -3799,7 +3799,7 @@
     <row r="94">
       <c r="A94" s="25" t="inlineStr">
         <is>
-          <t>Excel for managers</t>
+          <t>Dental group reporting</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="B97" s="20" t="n">
-        <v>8800</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="98">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="B98" s="20" t="n">
-        <v>-1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="B99" s="19" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100">
@@ -3896,7 +3896,7 @@
     <row r="106">
       <c r="A106" s="25" t="inlineStr">
         <is>
-          <t>Dental group reporting</t>
+          <t>Manufacturer process mapping</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="B109" s="20" t="n">
-        <v>6800</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="110">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="B110" s="20" t="n">
-        <v>0</v>
+        <v>-2200</v>
       </c>
     </row>
     <row r="111">
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="B111" s="19" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="112">
@@ -3993,7 +3993,7 @@
     <row r="118">
       <c r="A118" s="25" t="inlineStr">
         <is>
-          <t>Manufacturer process mapping</t>
+          <t>Logistics systems rollout</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="B121" s="20" t="n">
-        <v>20400</v>
+        <v>36750</v>
       </c>
     </row>
     <row r="122">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="B122" s="20" t="n">
-        <v>-2200</v>
+        <v>-11200</v>
       </c>
     </row>
     <row r="123">
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B123" s="19" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124">
@@ -4090,7 +4090,7 @@
     <row r="130">
       <c r="A130" s="25" t="inlineStr">
         <is>
-          <t>Logistics systems rollout</t>
+          <t>Excel for managers</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="B133" s="20" t="n">
-        <v>36750</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="134">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="B134" s="20" t="n">
-        <v>-4800</v>
+        <v>-4200</v>
       </c>
     </row>
     <row r="135">
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="B135" s="19" t="n">
-        <v>210</v>
+        <v>36</v>
       </c>
     </row>
     <row r="136">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="B147" s="19" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="148">

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -16,12 +16,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="Consultant_utilisation">'The fourth sheet'!$B$6</definedName>
+    <definedName name="Revenue_per_billable_hour">'The fourth sheet'!$B$7</definedName>
+    <definedName name="Unbilled_work_unpaid_invoices">'The fourth sheet'!$B$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'The fourth sheet'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'The fourth sheet'!$A$1:$D$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Profit and loss'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Profit and loss'!$A$1:$D$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Balance sheet'!$A$1:$D$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Engagements'!$A$6:$J$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cash flow'!$A$1:$D$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Engagements'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Engagements'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A$1:$C$151</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Assumptions'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,10 +38,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0;[Red](#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="+0.0&quot; pts&quot;;(0.0&quot; pts&quot;);&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="+#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -145,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,20 +167,22 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -201,6 +214,22 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Roboto"/>
+        <b val="1"/>
+        <color rgb="002F7A5D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Roboto"/>
+        <b val="1"/>
+        <color rgb="00B42318"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -271,6 +300,335 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Gross margin on each client engagement, September 2026 work only · target 40.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'The fourth sheet'!$A$14:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'The fourth sheet'!$B$14:$B$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Gross margin %, September engagements</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %, September engagements</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Engagements'!$B$7:$B$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Engagements'!$J$7:$J$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Engagements" displayName="Engagements" ref="A6:J25" headerRowCount="1">
+  <autoFilter ref="A6:J25"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Month"/>
+    <tableColumn id="2" name="Engagement"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Hours"/>
+    <tableColumn id="5" name="Revenue"/>
+    <tableColumn id="6" name="Billed"/>
+    <tableColumn id="7" name="Contractors"/>
+    <tableColumn id="8" name="Consultant time cost (incl. on-costs)"/>
+    <tableColumn id="9" name="Gross margin"/>
+    <tableColumn id="10" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -581,14 +939,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -629,8 +987,8 @@
         <f>Workings!C13</f>
         <v/>
       </c>
-      <c r="D6" s="5">
-        <f>B6-C6</f>
+      <c r="D6" s="6">
+        <f>(B6-C6)*100</f>
         <v/>
       </c>
     </row>
@@ -640,15 +998,15 @@
           <t>Revenue per billable hour</t>
         </is>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <f>Workings!B21</f>
         <v/>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <f>Workings!C21</f>
         <v/>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="8">
         <f>B7-C7</f>
         <v/>
       </c>
@@ -659,15 +1017,15 @@
           <t>Unbilled work + unpaid invoices</t>
         </is>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <f>Workings!B30</f>
         <v/>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <f>Workings!C30</f>
         <v/>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="8">
         <f>B8-C8</f>
         <v/>
       </c>
@@ -675,7 +1033,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Gross margin on each client engagement, September 2026 work only</t>
         </is>
@@ -711,7 +1069,7 @@
         <f>Workings!B43</f>
         <v/>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <f>Workings!B42</f>
         <v/>
       </c>
@@ -726,7 +1084,7 @@
         <f>Workings!B55</f>
         <v/>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <f>Workings!B54</f>
         <v/>
       </c>
@@ -741,7 +1099,7 @@
         <f>Workings!B67</f>
         <v/>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <f>Workings!B66</f>
         <v/>
       </c>
@@ -756,7 +1114,7 @@
         <f>Workings!B79</f>
         <v/>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <f>Workings!B78</f>
         <v/>
       </c>
@@ -771,7 +1129,7 @@
         <f>Workings!B91</f>
         <v/>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <f>Workings!B90</f>
         <v/>
       </c>
@@ -786,7 +1144,7 @@
         <f>Workings!B103</f>
         <v/>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <f>Workings!B102</f>
         <v/>
       </c>
@@ -801,7 +1159,7 @@
         <f>Workings!B115</f>
         <v/>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <f>Workings!B114</f>
         <v/>
       </c>
@@ -816,7 +1174,7 @@
         <f>Workings!B127</f>
         <v/>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
         <f>Workings!B126</f>
         <v/>
       </c>
@@ -831,7 +1189,7 @@
         <f>Workings!B139</f>
         <v/>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="7">
         <f>Workings!B138</f>
         <v/>
       </c>
@@ -846,13 +1204,13 @@
         <f>Workings!B151</f>
         <v/>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <f>Workings!B150</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
@@ -862,17 +1220,42 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -901,14 +1284,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -935,421 +1318,597 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Projects (hours worked)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>85950</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>75740</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="13">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>32500</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>32500</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="13">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>13400</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>6400</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="13">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="15">
         <f>SUM(B6:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <f>SUM(C6:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="16">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Cost of sales</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Consultant salaries (incl. on-costs)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>-46500</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>-46500</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="13">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>-17600</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>-6900</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="13">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Total cost of sales</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="15">
         <f>SUM(B11:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="15">
         <f>SUM(C11:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="16">
         <f>B13-C13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="15">
         <f>B9+B13</f>
         <v/>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <f>C9+C13</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="16">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Management and admin wages</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>-24000</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>-24000</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="13">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Marketing and business development</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="7" t="n">
         <v>-5800</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>-6500</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="13">
         <f>B17-C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Rent and occupancy</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="7" t="n">
         <v>-8000</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="7" t="n">
         <v>-8000</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="13">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>IT and software</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="7" t="n">
         <v>-4500</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>-4500</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="13">
         <f>B19-C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Professional indemnity insurance</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="7" t="n">
         <v>-2500</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>-2500</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="13">
         <f>B20-C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="7" t="n">
         <v>-1800</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>-2600</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="13">
         <f>B21-C21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Other overheads</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="7" t="n">
         <v>-3300</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>-3300</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="13">
         <f>B22-C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="15">
         <f>SUM(B16:B22)</f>
         <v/>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="15">
         <f>SUM(C16:C22)</f>
         <v/>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="16">
         <f>B23-C23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="15">
         <f>B14+B23</f>
         <v/>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="15">
         <f>C14+C23</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="16">
         <f>B24-C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="15" t="n">
         <v>-2000</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="15" t="n">
         <v>-2000</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="16">
         <f>B25-C25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="15" t="n">
         <v>-240</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="15" t="n">
         <v>-250</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="16">
         <f>B26-C26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="15">
         <f>B24+B25+B26</f>
         <v/>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="15">
         <f>C24+C25+C26</f>
         <v/>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="16">
         <f>B27-C27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Income tax provision (25%)</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="15" t="n">
         <v>-3903</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="15" t="n">
         <v>-1898</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="16">
         <f>B28-C28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Net profit after tax</t>
         </is>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="18">
         <f>B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="18">
         <f>C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="19">
         <f>B29-C29</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="cellIs" priority="25" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
+    <cfRule type="cellIs" priority="27" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
+    <cfRule type="cellIs" priority="29" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23">
+    <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24">
+    <cfRule type="cellIs" priority="33" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25">
+    <cfRule type="cellIs" priority="35" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26">
+    <cfRule type="cellIs" priority="37" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="38" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27">
+    <cfRule type="cellIs" priority="39" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="40" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28">
+    <cfRule type="cellIs" priority="41" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29">
+    <cfRule type="cellIs" priority="43" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="44" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1383,14 +1942,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1417,323 +1976,323 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Current assets</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>149260</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>192150</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="13">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Trade debtors (unpaid invoices)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>116800</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>71290</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="13">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Work in progress (unbilled project time)</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>99290</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>77900</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="13">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Prepayments</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="13">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="15">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="15">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="16">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Office equipment</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="15" t="n">
         <v>60200</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="15" t="n">
         <v>59000</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="16">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="15">
         <f>B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="15">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="16">
         <f>B12-C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Current liabilities</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Trade creditors (bills due next month)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <v>17600</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>6900</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="13">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Employee leave provisions</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>122300</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>121700</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="13">
         <f>B15-C15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Income tax payable</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>54301</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>50398</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="13">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="15">
         <f>SUM(B14:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="15">
         <f>SUM(C14:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="16">
         <f>B17-C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Equipment finance</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="15" t="n">
         <v>14600</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="15" t="n">
         <v>16300</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="16">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="15">
         <f>B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="15">
         <f>C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="16">
         <f>B19-C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Net assets</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="18">
         <f>B12-B19</f>
         <v/>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="18">
         <f>C12-C19</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="19">
         <f>B20-C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Share capital</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="13">
         <f>B22-C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Retained earnings</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="7" t="n">
         <v>211749</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="7" t="n">
         <v>200042</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="13">
         <f>B23-C23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="18">
         <f>SUM(B22:B23)</f>
         <v/>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="18">
         <f>SUM(C22:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="19">
         <f>B24-C24</f>
         <v/>
       </c>
@@ -1744,7 +2303,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1778,14 +2337,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1812,264 +2371,368 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Operating activities</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Receipts from customers (invoices paid)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>64950</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>137200</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="13">
         <f>B6-C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Payments to contractors and suppliers</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>-32800</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>-31300</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="13">
         <f>B7-C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Payments to employees</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>-69900</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>-69800</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="13">
         <f>B8-C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>-240</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>-250</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="13">
         <f>B9-C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="13">
         <f>B10-C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="15">
         <f>SUM(B6:B10)</f>
         <v/>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="15">
         <f>SUM(C6:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="16">
         <f>B11-C11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Investing activities</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>-3200</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="13">
         <f>B13-C13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Net cash from investing activities</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="15">
         <f>SUM(B13:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <f>SUM(C13:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="16">
         <f>B14-C14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Financing activities</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Equipment finance repaid</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>-1700</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>-1700</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="13">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Net cash from financing activities</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="15">
         <f>SUM(B16:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="15">
         <f>SUM(C16:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="16">
         <f>B17-C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="15">
         <f>B11+B14+B17</f>
         <v/>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="15">
         <f>C11+C14+C17</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="16">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Cash at start of month</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="15" t="n">
         <v>192150</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="15" t="n">
         <v>158000</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="16">
         <f>B19-C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Cash at end of month</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="18">
         <f>B19+B18</f>
         <v/>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="18">
         <f>C19+C18</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="19">
         <f>B20-C20</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="cellIs" priority="25" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2109,14 +2772,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2789,7 @@
           <t>Consultant cost rate ($ per hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="7" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2184,828 +2847,831 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Agribusiness CFO support</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="22">
         <f>D7*$B$4</f>
         <v/>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="22">
         <f>E7-G7-H7</f>
         <v/>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="23">
         <f>IF(E7=0,"",I7/E7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Construction firm finance</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>58</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="22" t="n">
         <v>9500</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="22" t="n">
         <v>9500</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="22">
         <f>D8*$B$4</f>
         <v/>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="22">
         <f>E8-G8-H8</f>
         <v/>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="23">
         <f>IF(E8=0,"",I8/E8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Dental group reporting</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>44</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="22" t="n">
         <v>6800</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="22" t="n">
         <v>6800</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="22">
         <f>D9*$B$4</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="22">
         <f>E9-G9-H9</f>
         <v/>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="23">
         <f>IF(E9=0,"",I9/E9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Excel for managers</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="22" t="n">
         <v>8800</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="22" t="n">
         <v>8800</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="22">
         <f>D10*$B$4</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="22">
         <f>E10-G10-H10</f>
         <v/>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="23">
         <f>IF(E10=0,"",I10/E10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Health charity board pack</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>64</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="22" t="n">
         <v>10560</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="22" t="n">
         <v>10560</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="22">
         <f>D11*$B$4</f>
         <v/>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="22">
         <f>E11-G11-H11</f>
         <v/>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="23">
         <f>IF(E11=0,"",I11/E11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Hospitality payroll</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="22">
         <f>D12*$B$4</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="22">
         <f>E12-G12-H12</f>
         <v/>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="23">
         <f>IF(E12=0,"",I12/E12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Logistics systems rollout</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="21" t="n">
         <v>210</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="22" t="n">
         <v>36750</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="22" t="n">
         <v>30000</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="22" t="n">
         <v>11200</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="22">
         <f>D13*$B$4</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="22">
         <f>E13-G13-H13</f>
         <v/>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="23">
         <f>IF(E13=0,"",I13/E13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Manufacturer process mapping</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="21" t="n">
         <v>120</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="22" t="n">
         <v>20400</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="22" t="n">
         <v>24000</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="22" t="n">
         <v>2200</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="22">
         <f>D14*$B$4</f>
         <v/>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="22">
         <f>E14-G14-H14</f>
         <v/>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="23">
         <f>IF(E14=0,"",I14/E14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Power BI basics</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="22" t="n">
         <v>4600</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="22" t="n">
         <v>4600</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="22">
         <f>D15*$B$4</f>
         <v/>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="22">
         <f>E15-G15-H15</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="23">
         <f>IF(E15=0,"",I15/E15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Retail pricing review</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="21" t="n">
         <v>96</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="22" t="n">
         <v>18240</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="22">
         <f>D16*$B$4</f>
         <v/>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="22">
         <f>E16-G16-H16</f>
         <v/>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="23">
         <f>IF(E16=0,"",I16/E16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Agribusiness CFO support</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="21" t="n">
         <v>68</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F17" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="22">
         <f>D17*$B$4</f>
         <v/>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="22">
         <f>E17-G17-H17</f>
         <v/>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="23">
         <f>IF(E17=0,"",I17/E17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Budgeting workshop</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="22" t="n">
         <v>6400</v>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F18" s="22" t="n">
         <v>6400</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="22" t="n">
         <v>900</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="22">
         <f>D18*$B$4</f>
         <v/>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="22">
         <f>E18-G18-H18</f>
         <v/>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="23">
         <f>IF(E18=0,"",I18/E18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Construction firm finance</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="21" t="n">
         <v>56</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="22" t="n">
         <v>9500</v>
       </c>
-      <c r="F19" s="20" t="n">
+      <c r="F19" s="22" t="n">
         <v>9500</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="22">
         <f>D19*$B$4</f>
         <v/>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="22">
         <f>E19-G19-H19</f>
         <v/>
       </c>
-      <c r="J19" s="21">
+      <c r="J19" s="23">
         <f>IF(E19=0,"",I19/E19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Dental group reporting</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E20" s="22" t="n">
         <v>6800</v>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F20" s="22" t="n">
         <v>6800</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="22">
         <f>D20*$B$4</f>
         <v/>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="22">
         <f>E20-G20-H20</f>
         <v/>
       </c>
-      <c r="J20" s="21">
+      <c r="J20" s="23">
         <f>IF(E20=0,"",I20/E20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Distributor cost-to-serve</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="21" t="n">
         <v>88</v>
       </c>
-      <c r="E21" s="20" t="n">
+      <c r="E21" s="22" t="n">
         <v>15840</v>
       </c>
-      <c r="F21" s="20" t="n">
+      <c r="F21" s="22" t="n">
         <v>15840</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G21" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="22">
         <f>D21*$B$4</f>
         <v/>
       </c>
-      <c r="I21" s="20">
+      <c r="I21" s="22">
         <f>E21-G21-H21</f>
         <v/>
       </c>
-      <c r="J21" s="21">
+      <c r="J21" s="23">
         <f>IF(E21=0,"",I21/E21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Hospitality payroll</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>Retainer</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="F22" s="20" t="n">
+      <c r="F22" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="22">
         <f>D22*$B$4</f>
         <v/>
       </c>
-      <c r="I22" s="20">
+      <c r="I22" s="22">
         <f>E22-G22-H22</f>
         <v/>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="23">
         <f>IF(E22=0,"",I22/E22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Logistics systems rollout</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="21" t="n">
         <v>180</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="22" t="n">
         <v>31500</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="22">
         <f>D23*$B$4</f>
         <v/>
       </c>
-      <c r="I23" s="20">
+      <c r="I23" s="22">
         <f>E23-G23-H23</f>
         <v/>
       </c>
-      <c r="J23" s="21">
+      <c r="J23" s="23">
         <f>IF(E23=0,"",I23/E23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Manufacturer process mapping</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="22" t="n">
         <v>17000</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="22" t="n">
         <v>1800</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="22">
         <f>D24*$B$4</f>
         <v/>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="22">
         <f>E24-G24-H24</f>
         <v/>
       </c>
-      <c r="J24" s="21">
+      <c r="J24" s="23">
         <f>IF(E24=0,"",I24/E24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Retail pricing review</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="22" t="n">
         <v>11400</v>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="22">
         <f>D25*$B$4</f>
         <v/>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="22">
         <f>E25-G25-H25</f>
         <v/>
       </c>
-      <c r="J25" s="21">
+      <c r="J25" s="23">
         <f>IF(E25=0,"",I25/E25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="25">
         <f>SUM(D7:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="26">
         <f>SUM(E7:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="26">
         <f>SUM(F7:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="26">
         <f>SUM(G7:G25)</f>
         <v/>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="26">
         <f>SUM(H7:H25)</f>
         <v/>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="26">
         <f>SUM(I7:I25)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:J25"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3034,27 +3700,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Consultant utilisation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Billable hours ÷ hours available</t>
         </is>
@@ -3079,10 +3745,10 @@
           <t>Billable hours (timesheets)</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="21" t="n">
         <v>764</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="21" t="n">
         <v>662</v>
       </c>
     </row>
@@ -3092,10 +3758,10 @@
           <t>Consultants</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3105,10 +3771,10 @@
           <t>Working days</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3118,10 +3784,10 @@
           <t>Hours per day</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="21" t="n">
         <v>7.6</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>7.6</v>
       </c>
     </row>
@@ -3131,26 +3797,26 @@
           <t>Hours available</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="21">
         <f>B9*B10*B11</f>
         <v/>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="21">
         <f>C9*C10*C11</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Utilisation</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="29">
         <f>B8/B12</f>
         <v/>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="29">
         <f>C8/C12</f>
         <v/>
       </c>
@@ -3158,14 +3824,14 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Revenue per billable hour</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Revenue ÷ billable hours</t>
         </is>
@@ -3190,10 +3856,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="22" t="n">
         <v>131850</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="22" t="n">
         <v>114640</v>
       </c>
     </row>
@@ -3203,24 +3869,24 @@
           <t>Billable hours</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="21" t="n">
         <v>764</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="21" t="n">
         <v>662</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Revenue per hour</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="30">
         <f>B19/B20</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="30">
         <f>C19/C20</f>
         <v/>
       </c>
@@ -3235,14 +3901,14 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Cash tied up in work</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Work in progress + unpaid invoices at month end</t>
         </is>
@@ -3267,10 +3933,10 @@
           <t>Work in progress (project time not yet billed)</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="22" t="n">
         <v>99290</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="22" t="n">
         <v>77900</v>
       </c>
     </row>
@@ -3280,24 +3946,24 @@
           <t>Unpaid client invoices</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="22" t="n">
         <v>116800</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="22" t="n">
         <v>71290</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>Total tied up</t>
         </is>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="30">
         <f>B28+B29</f>
         <v/>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="30">
         <f>C28+C29</f>
         <v/>
       </c>
@@ -3312,14 +3978,14 @@
     <row r="32"/>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Power BI basics</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -3339,7 +4005,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
+      <c r="B37" s="22" t="n">
         <v>4600</v>
       </c>
     </row>
@@ -3349,7 +4015,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
+      <c r="B38" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3359,7 +4025,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n">
+      <c r="B39" s="21" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3369,7 +4035,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
+      <c r="B40" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3379,7 +4045,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="22">
         <f>-B39*B40</f>
         <v/>
       </c>
@@ -3390,18 +4056,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="22">
         <f>B37+B38+B41</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="29">
         <f>B42/B37</f>
         <v/>
       </c>
@@ -3409,14 +4075,14 @@
     <row r="44"/>
     <row r="45"/>
     <row r="46">
-      <c r="A46" s="25" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>Retail pricing review</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -3436,7 +4102,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n">
+      <c r="B49" s="22" t="n">
         <v>18240</v>
       </c>
     </row>
@@ -3446,7 +4112,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n">
+      <c r="B50" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3456,7 +4122,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B51" s="19" t="n">
+      <c r="B51" s="21" t="n">
         <v>96</v>
       </c>
     </row>
@@ -3466,7 +4132,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n">
+      <c r="B52" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3476,7 +4142,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="22">
         <f>-B51*B52</f>
         <v/>
       </c>
@@ -3487,18 +4153,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="22">
         <f>B49+B50+B53</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B55" s="27">
+      <c r="B55" s="29">
         <f>B54/B49</f>
         <v/>
       </c>
@@ -3506,14 +4172,14 @@
     <row r="56"/>
     <row r="57"/>
     <row r="58">
-      <c r="A58" s="25" t="inlineStr">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>Agribusiness CFO support</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -3533,7 +4199,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n">
+      <c r="B61" s="22" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -3543,7 +4209,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B62" s="20" t="n">
+      <c r="B62" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3553,7 +4219,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B63" s="19" t="n">
+      <c r="B63" s="21" t="n">
         <v>70</v>
       </c>
     </row>
@@ -3563,7 +4229,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B64" s="20" t="n">
+      <c r="B64" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3573,7 +4239,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="22">
         <f>-B63*B64</f>
         <v/>
       </c>
@@ -3584,18 +4250,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="22">
         <f>B61+B62+B65</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B67" s="27">
+      <c r="B67" s="29">
         <f>B66/B61</f>
         <v/>
       </c>
@@ -3603,14 +4269,14 @@
     <row r="68"/>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="25" t="inlineStr">
+      <c r="A70" s="27" t="inlineStr">
         <is>
           <t>Health charity board pack</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -3630,7 +4296,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n">
+      <c r="B73" s="22" t="n">
         <v>10560</v>
       </c>
     </row>
@@ -3640,7 +4306,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B74" s="20" t="n">
+      <c r="B74" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3650,7 +4316,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B75" s="19" t="n">
+      <c r="B75" s="21" t="n">
         <v>64</v>
       </c>
     </row>
@@ -3660,7 +4326,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n">
+      <c r="B76" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3670,7 +4336,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B77" s="20">
+      <c r="B77" s="22">
         <f>-B75*B76</f>
         <v/>
       </c>
@@ -3681,18 +4347,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B78" s="20">
+      <c r="B78" s="22">
         <f>B73+B74+B77</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="26" t="inlineStr">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B79" s="27">
+      <c r="B79" s="29">
         <f>B78/B73</f>
         <v/>
       </c>
@@ -3700,14 +4366,14 @@
     <row r="80"/>
     <row r="81"/>
     <row r="82">
-      <c r="A82" s="25" t="inlineStr">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>Construction firm finance</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -3727,7 +4393,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B85" s="20" t="n">
+      <c r="B85" s="22" t="n">
         <v>9500</v>
       </c>
     </row>
@@ -3737,7 +4403,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B86" s="20" t="n">
+      <c r="B86" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3747,7 +4413,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B87" s="19" t="n">
+      <c r="B87" s="21" t="n">
         <v>58</v>
       </c>
     </row>
@@ -3757,7 +4423,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B88" s="20" t="n">
+      <c r="B88" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3767,7 +4433,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B89" s="20">
+      <c r="B89" s="22">
         <f>-B87*B88</f>
         <v/>
       </c>
@@ -3778,18 +4444,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B90" s="20">
+      <c r="B90" s="22">
         <f>B85+B86+B89</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="26" t="inlineStr">
+      <c r="A91" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B91" s="27">
+      <c r="B91" s="29">
         <f>B90/B85</f>
         <v/>
       </c>
@@ -3797,14 +4463,14 @@
     <row r="92"/>
     <row r="93"/>
     <row r="94">
-      <c r="A94" s="25" t="inlineStr">
+      <c r="A94" s="27" t="inlineStr">
         <is>
           <t>Dental group reporting</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -3824,7 +4490,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B97" s="20" t="n">
+      <c r="B97" s="22" t="n">
         <v>6800</v>
       </c>
     </row>
@@ -3834,7 +4500,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B98" s="20" t="n">
+      <c r="B98" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3844,7 +4510,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B99" s="19" t="n">
+      <c r="B99" s="21" t="n">
         <v>44</v>
       </c>
     </row>
@@ -3854,7 +4520,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B100" s="20" t="n">
+      <c r="B100" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3864,7 +4530,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B101" s="20">
+      <c r="B101" s="22">
         <f>-B99*B100</f>
         <v/>
       </c>
@@ -3875,18 +4541,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B102" s="20">
+      <c r="B102" s="22">
         <f>B97+B98+B101</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="26" t="inlineStr">
+      <c r="A103" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B103" s="27">
+      <c r="B103" s="29">
         <f>B102/B97</f>
         <v/>
       </c>
@@ -3894,14 +4560,14 @@
     <row r="104"/>
     <row r="105"/>
     <row r="106">
-      <c r="A106" s="25" t="inlineStr">
+      <c r="A106" s="27" t="inlineStr">
         <is>
           <t>Manufacturer process mapping</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -3921,7 +4587,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B109" s="20" t="n">
+      <c r="B109" s="22" t="n">
         <v>20400</v>
       </c>
     </row>
@@ -3931,7 +4597,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B110" s="20" t="n">
+      <c r="B110" s="22" t="n">
         <v>-2200</v>
       </c>
     </row>
@@ -3941,7 +4607,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B111" s="19" t="n">
+      <c r="B111" s="21" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3951,7 +4617,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B112" s="20" t="n">
+      <c r="B112" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3961,7 +4627,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B113" s="20">
+      <c r="B113" s="22">
         <f>-B111*B112</f>
         <v/>
       </c>
@@ -3972,18 +4638,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B114" s="20">
+      <c r="B114" s="22">
         <f>B109+B110+B113</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="26" t="inlineStr">
+      <c r="A115" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B115" s="27">
+      <c r="B115" s="29">
         <f>B114/B109</f>
         <v/>
       </c>
@@ -3991,14 +4657,14 @@
     <row r="116"/>
     <row r="117"/>
     <row r="118">
-      <c r="A118" s="25" t="inlineStr">
+      <c r="A118" s="27" t="inlineStr">
         <is>
           <t>Logistics systems rollout</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -4018,7 +4684,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B121" s="20" t="n">
+      <c r="B121" s="22" t="n">
         <v>36750</v>
       </c>
     </row>
@@ -4028,7 +4694,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B122" s="20" t="n">
+      <c r="B122" s="22" t="n">
         <v>-11200</v>
       </c>
     </row>
@@ -4038,7 +4704,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B123" s="19" t="n">
+      <c r="B123" s="21" t="n">
         <v>210</v>
       </c>
     </row>
@@ -4048,7 +4714,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B124" s="20" t="n">
+      <c r="B124" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4058,7 +4724,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B125" s="20">
+      <c r="B125" s="22">
         <f>-B123*B124</f>
         <v/>
       </c>
@@ -4069,18 +4735,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B126" s="20">
+      <c r="B126" s="22">
         <f>B121+B122+B125</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="26" t="inlineStr">
+      <c r="A127" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B127" s="27">
+      <c r="B127" s="29">
         <f>B126/B121</f>
         <v/>
       </c>
@@ -4088,14 +4754,14 @@
     <row r="128"/>
     <row r="129"/>
     <row r="130">
-      <c r="A130" s="25" t="inlineStr">
+      <c r="A130" s="27" t="inlineStr">
         <is>
           <t>Excel for managers</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -4115,7 +4781,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B133" s="20" t="n">
+      <c r="B133" s="22" t="n">
         <v>8800</v>
       </c>
     </row>
@@ -4125,7 +4791,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B134" s="20" t="n">
+      <c r="B134" s="22" t="n">
         <v>-4200</v>
       </c>
     </row>
@@ -4135,7 +4801,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B135" s="19" t="n">
+      <c r="B135" s="21" t="n">
         <v>36</v>
       </c>
     </row>
@@ -4145,7 +4811,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B136" s="20" t="n">
+      <c r="B136" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4155,7 +4821,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B137" s="20">
+      <c r="B137" s="22">
         <f>-B135*B136</f>
         <v/>
       </c>
@@ -4166,18 +4832,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B138" s="20">
+      <c r="B138" s="22">
         <f>B133+B134+B137</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="26" t="inlineStr">
+      <c r="A139" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B139" s="27">
+      <c r="B139" s="29">
         <f>B138/B133</f>
         <v/>
       </c>
@@ -4185,14 +4851,14 @@
     <row r="140"/>
     <row r="141"/>
     <row r="142">
-      <c r="A142" s="25" t="inlineStr">
+      <c r="A142" s="27" t="inlineStr">
         <is>
           <t>Hospitality payroll</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="A143" s="10" t="inlineStr">
         <is>
           <t>Gross margin ÷ revenue for this engagement (before overheads)</t>
         </is>
@@ -4212,7 +4878,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B145" s="20" t="n">
+      <c r="B145" s="22" t="n">
         <v>4200</v>
       </c>
     </row>
@@ -4222,7 +4888,7 @@
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B146" s="20" t="n">
+      <c r="B146" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4232,7 +4898,7 @@
           <t>Consultant hours</t>
         </is>
       </c>
-      <c r="B147" s="19" t="n">
+      <c r="B147" s="21" t="n">
         <v>52</v>
       </c>
     </row>
@@ -4242,7 +4908,7 @@
           <t>Consultant cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B148" s="20" t="n">
+      <c r="B148" s="22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4252,7 +4918,7 @@
           <t>Consultant time</t>
         </is>
       </c>
-      <c r="B149" s="20">
+      <c r="B149" s="22">
         <f>-B147*B148</f>
         <v/>
       </c>
@@ -4263,18 +4929,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B150" s="20">
+      <c r="B150" s="22">
         <f>B145+B146+B149</f>
         <v/>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="26" t="inlineStr">
+      <c r="A151" s="28" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B151" s="27">
+      <c r="B151" s="29">
         <f>B150/B145</f>
         <v/>
       </c>
@@ -4288,7 +4954,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4328,56 +4994,56 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Advisory Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>The business</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>A Brisbane finance and operations consultancy: projects billed on milestones, monthly retainers and training. 6 consultants, 3 management and admin staff.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Reporting month</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>September 2026, compared with August 2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Financial year</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>FY2027: 1 July 2026 to 30 June 2027</t>
         </is>
@@ -4385,55 +5051,55 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Engagements (September)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>hours worked at each project's rate; billed on milestones (unbilled time = work in progress)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>fixed monthly fee, billed monthly</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>fixed fee, billed on delivery</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Engagements in September</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>10 (every one is in the Excel download and CSV)</t>
         </is>
@@ -4441,55 +5107,55 @@
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Costs</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Consultants</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>6 on salary: $46,500 a month incl. on-costs</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Engagement costing rate</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>$60/hour for consultant time</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Working days</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>20 in August (Ekka show holiday), 22 in September; 7.6 hours a day</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>25% of profit, provided monthly</t>
         </is>
@@ -4497,43 +5163,43 @@
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Cash and balance sheet</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Client payments</t>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>each invoice is paid on its own date; unpaid invoices at month end = debtors</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Contractors</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>paid the following month</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>excluded throughout, for simplicity</t>
         </is>
@@ -4541,7 +5207,7 @@
     </row>
     <row r="26"/>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Checks (all passed)</t>
         </is>
@@ -4589,8 +5255,9 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Print check (done before this file was saved)</t>
         </is>
@@ -4651,7 +5318,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The fourth sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit and loss" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart lines" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit and loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Consultant_utilisation">'The fourth sheet'!$B$6</definedName>
@@ -21,16 +22,16 @@
     <definedName name="Unbilled_work_unpaid_invoices">'The fourth sheet'!$B$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'The fourth sheet'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'The fourth sheet'!$A$1:$D$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Profit and loss'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Profit and loss'!$A$1:$D$29</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Balance sheet'!$A$1:$D$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cash flow'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Engagements'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Engagements'!$A$1:$J$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A$1:$C$151</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Assumptions'!$A$1:$B$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Profit and loss'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Profit and loss'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Balance sheet'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Balance sheet'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cash flow'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Engagements'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Engagements'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Workings'!$A$1:$C$151</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Assumptions'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -326,7 +327,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Gross margin on each client engagement, September 2026 work only · target 40.0%</a:t>
+              <a:t>Gross margin on each client engagement, September 2026 work only</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -421,6 +422,82 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 40.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$4:$B$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$4:$C$5</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -436,6 +513,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.93955"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -443,6 +522,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.93955"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -567,7 +673,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3420000"/>
+    <ext cx="5400000" cy="3636000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -946,7 +1052,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1355,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1260,6 +1366,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Points for the target and break-even lines drawn on the charts (hidden sheet; edit the values on the chart's own sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The fourth sheet: Gross margin on each client engagement, September 2026 work only: Target 40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1291,7 +1442,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -1908,7 +2059,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1917,7 +2068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1949,7 +2100,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2454,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2312,7 +2463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2344,7 +2495,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2883,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2741,7 +2892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2779,7 +2930,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3813,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3675,7 +3826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3707,7 +3858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -4954,7 +5105,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4971,7 +5122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5001,7 +5152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5469,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -1052,7 +1052,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1442,7 +1442,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2100,7 +2100,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2495,7 +2495,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2930,7 +2930,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3858,7 +3858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5152,7 +5152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>10 (every one is in the Excel download and CSV)</t>
+          <t>10 (every one is in the spreadsheet download and CSV)</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5469,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -25,13 +25,13 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Profit and loss'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Profit and loss'!$A$1:$D$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Balance sheet'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Balance sheet'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Balance sheet'!$A$1:$D$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cash flow'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow'!$A$1:$D$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Engagements'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Engagements'!$A$1:$J$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Workings'!$A$1:$C$151</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Assumptions'!$A$1:$B$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Assumptions'!$A$1:$B$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -358,20 +358,6 @@
           </spPr>
           <invertIfNegative val="0"/>
           <dPt>
-            <idx val="7"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
             <idx val="8"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -513,7 +499,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.93955"/>
+          <max val="0.9602499999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -527,7 +513,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.93955"/>
+          <max val="0.9602499999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1052,7 +1038,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1341,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1442,7 +1428,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
         </is>
       </c>
     </row>
@@ -1482,10 +1468,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>85950</v>
+        <v>94830</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>75740</v>
+        <v>83800</v>
       </c>
       <c r="D6" s="13">
         <f>B6-C6</f>
@@ -1499,10 +1485,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="D7" s="13">
         <f>B7-C7</f>
@@ -1516,10 +1502,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13400</v>
+        <v>14800</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="D8" s="13">
         <f>B8-C8</f>
@@ -1559,10 +1545,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>-46500</v>
+        <v>-60192</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-46500</v>
+        <v>-54720</v>
       </c>
       <c r="D11" s="13">
         <f>B11-C11</f>
@@ -1848,10 +1834,10 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>-3903</v>
+        <v>-3850</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>-1898</v>
+        <v>-2808</v>
       </c>
       <c r="D28" s="16">
         <f>B28-C28</f>
@@ -2059,7 +2045,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2074,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2100,7 +2086,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
         </is>
       </c>
     </row>
@@ -2140,10 +2126,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>149260</v>
+        <v>207781</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>192150</v>
+        <v>229278</v>
       </c>
       <c r="D6" s="13">
         <f>B6-C6</f>
@@ -2157,10 +2143,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>116800</v>
+        <v>141592</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>71290</v>
+        <v>86405</v>
       </c>
       <c r="D7" s="13">
         <f>B7-C7</f>
@@ -2174,10 +2160,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>99290</v>
+        <v>109810</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>77900</v>
+        <v>86000</v>
       </c>
       <c r="D8" s="13">
         <f>B8-C8</f>
@@ -2270,10 +2256,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>17600</v>
+        <v>19360</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6900</v>
+        <v>7590</v>
       </c>
       <c r="D14" s="13">
         <f>B14-C14</f>
@@ -2283,14 +2269,14 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Employee leave provisions</t>
+          <t>Wages owed (since the last pay run)</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>122300</v>
+        <v>31400</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>121700</v>
+        <v>23174</v>
       </c>
       <c r="D15" s="13">
         <f>B15-C15</f>
@@ -2300,14 +2286,14 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Income tax payable</t>
+          <t>Super payable</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>54301</v>
+        <v>3766</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>50398</v>
+        <v>2780</v>
       </c>
       <c r="D16" s="13">
         <f>B16-C16</f>
@@ -2315,116 +2301,124 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>PAYG withholding payable</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>47814</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>31876</v>
+      </c>
+      <c r="D17" s="13">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>GST payable (net)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>20412</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>12930</v>
+      </c>
+      <c r="D18" s="13">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Employee leave provisions</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>122300</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>121700</v>
+      </c>
+      <c r="D19" s="13">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Income tax payable</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>55158</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>51308</v>
+      </c>
+      <c r="D20" s="13">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="B17" s="15">
-        <f>SUM(B14:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="15">
-        <f>SUM(C14:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="16">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="B21" s="15">
+        <f>SUM(B14:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>SUM(C14:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="16">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Equipment finance</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B22" s="15" t="n">
         <v>14600</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C22" s="15" t="n">
         <v>16300</v>
       </c>
-      <c r="D18" s="16">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="D22" s="16">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B19" s="15">
-        <f>B17+B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="15">
-        <f>C17+C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Net assets</t>
-        </is>
-      </c>
-      <c r="B20" s="18">
-        <f>B12-B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="18">
-        <f>C12-C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="19">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D22" s="13">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>211749</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>200042</v>
-      </c>
-      <c r="D23" s="13">
+      <c r="B23" s="15">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="15">
+        <f>C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
         <f>B23-C23</f>
         <v/>
       </c>
@@ -2432,19 +2426,79 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Total equity</t>
+          <t>Net assets</t>
         </is>
       </c>
       <c r="B24" s="18">
-        <f>SUM(B22:B23)</f>
+        <f>B12-B23</f>
         <v/>
       </c>
       <c r="C24" s="18">
-        <f>SUM(C22:C23)</f>
+        <f>C12-C23</f>
         <v/>
       </c>
       <c r="D24" s="19">
         <f>B24-C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D26" s="13">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>199573</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>188025</v>
+      </c>
+      <c r="D27" s="13">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B28" s="18">
+        <f>SUM(B26:B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="18">
+        <f>SUM(C26:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>B28-C28</f>
         <v/>
       </c>
     </row>
@@ -2454,7 +2508,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2495,7 +2549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
         </is>
       </c>
     </row>
@@ -2535,10 +2589,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>64950</v>
+        <v>78485</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>137200</v>
+        <v>166100</v>
       </c>
       <c r="D6" s="13">
         <f>B6-C6</f>
@@ -2552,10 +2606,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-32800</v>
+        <v>-36080</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-31300</v>
+        <v>-34430</v>
       </c>
       <c r="D7" s="13">
         <f>B7-C7</f>
@@ -2569,10 +2623,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>-69900</v>
+        <v>-58442</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>-69800</v>
+        <v>-58442</v>
       </c>
       <c r="D8" s="13">
         <f>B8-C8</f>
@@ -2599,7 +2653,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Income tax paid</t>
+          <t>GST, PAYG and income tax paid (BAS)</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -2646,7 +2700,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>-3200</v>
+        <v>-3520</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -2744,7 +2798,7 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>192150</v>
+        <v>229278</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>158000</v>
@@ -2883,7 +2937,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2930,7 +2984,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
         </is>
       </c>
     </row>
@@ -3017,10 +3071,10 @@
         <v>70</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>12000</v>
+        <v>13200</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>12000</v>
+        <v>13200</v>
       </c>
       <c r="G7" s="22" t="n">
         <v>0</v>
@@ -3058,10 +3112,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>9500</v>
+        <v>10400</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>9500</v>
+        <v>10400</v>
       </c>
       <c r="G8" s="22" t="n">
         <v>0</v>
@@ -3099,10 +3153,10 @@
         <v>44</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>6800</v>
+        <v>7500</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>6800</v>
+        <v>7500</v>
       </c>
       <c r="G9" s="22" t="n">
         <v>0</v>
@@ -3140,10 +3194,10 @@
         <v>36</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="G10" s="22" t="n">
         <v>4200</v>
@@ -3181,10 +3235,10 @@
         <v>64</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>10560</v>
+        <v>11520</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>10560</v>
+        <v>11520</v>
       </c>
       <c r="G11" s="22" t="n">
         <v>0</v>
@@ -3222,10 +3276,10 @@
         <v>52</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="G12" s="22" t="n">
         <v>0</v>
@@ -3263,10 +3317,10 @@
         <v>210</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>36750</v>
+        <v>40950</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>30000</v>
+        <v>33400</v>
       </c>
       <c r="G13" s="22" t="n">
         <v>11200</v>
@@ -3304,10 +3358,10 @@
         <v>120</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>20400</v>
+        <v>22200</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>24000</v>
+        <v>26100</v>
       </c>
       <c r="G14" s="22" t="n">
         <v>2200</v>
@@ -3345,10 +3399,10 @@
         <v>14</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="G15" s="22" t="n">
         <v>0</v>
@@ -3386,7 +3440,7 @@
         <v>96</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>18240</v>
+        <v>20160</v>
       </c>
       <c r="F16" s="22" t="n">
         <v>0</v>
@@ -3427,10 +3481,10 @@
         <v>68</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>12000</v>
+        <v>13200</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>12000</v>
+        <v>13200</v>
       </c>
       <c r="G17" s="22" t="n">
         <v>0</v>
@@ -3468,10 +3522,10 @@
         <v>20</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="G18" s="22" t="n">
         <v>900</v>
@@ -3509,10 +3563,10 @@
         <v>56</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>9500</v>
+        <v>10400</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>9500</v>
+        <v>10400</v>
       </c>
       <c r="G19" s="22" t="n">
         <v>0</v>
@@ -3550,10 +3604,10 @@
         <v>42</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>6800</v>
+        <v>7500</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>6800</v>
+        <v>7500</v>
       </c>
       <c r="G20" s="22" t="n">
         <v>0</v>
@@ -3591,10 +3645,10 @@
         <v>88</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>15840</v>
+        <v>17600</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>15840</v>
+        <v>17600</v>
       </c>
       <c r="G21" s="22" t="n">
         <v>0</v>
@@ -3632,10 +3686,10 @@
         <v>48</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="G22" s="22" t="n">
         <v>0</v>
@@ -3673,7 +3727,7 @@
         <v>180</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>31500</v>
+        <v>35100</v>
       </c>
       <c r="F23" s="22" t="n">
         <v>0</v>
@@ -3714,7 +3768,7 @@
         <v>100</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>17000</v>
+        <v>18500</v>
       </c>
       <c r="F24" s="22" t="n">
         <v>0</v>
@@ -3755,7 +3809,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="F25" s="22" t="n">
         <v>0</v>
@@ -3813,7 +3867,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3858,7 +3912,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
         </is>
       </c>
     </row>
@@ -4008,10 +4062,10 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>131850</v>
+        <v>145330</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>114640</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="20">
@@ -4085,10 +4139,10 @@
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>99290</v>
+        <v>109810</v>
       </c>
       <c r="C28" s="22" t="n">
-        <v>77900</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="29">
@@ -4098,10 +4152,10 @@
         </is>
       </c>
       <c r="B29" s="22" t="n">
-        <v>116800</v>
+        <v>141592</v>
       </c>
       <c r="C29" s="22" t="n">
-        <v>71290</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="30">
@@ -4157,7 +4211,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="38">
@@ -4254,7 +4308,7 @@
         </is>
       </c>
       <c r="B49" s="22" t="n">
-        <v>18240</v>
+        <v>20160</v>
       </c>
     </row>
     <row r="50">
@@ -4351,7 +4405,7 @@
         </is>
       </c>
       <c r="B61" s="22" t="n">
-        <v>12000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="62">
@@ -4448,7 +4502,7 @@
         </is>
       </c>
       <c r="B73" s="22" t="n">
-        <v>10560</v>
+        <v>11520</v>
       </c>
     </row>
     <row r="74">
@@ -4545,7 +4599,7 @@
         </is>
       </c>
       <c r="B85" s="22" t="n">
-        <v>9500</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="86">
@@ -4642,7 +4696,7 @@
         </is>
       </c>
       <c r="B97" s="22" t="n">
-        <v>6800</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="98">
@@ -4739,7 +4793,7 @@
         </is>
       </c>
       <c r="B109" s="22" t="n">
-        <v>20400</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="110">
@@ -4836,7 +4890,7 @@
         </is>
       </c>
       <c r="B121" s="22" t="n">
-        <v>36750</v>
+        <v>40950</v>
       </c>
     </row>
     <row r="122">
@@ -4933,7 +4987,7 @@
         </is>
       </c>
       <c r="B133" s="22" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="134">
@@ -5030,7 +5084,7 @@
         </is>
       </c>
       <c r="B145" s="22" t="n">
-        <v>4200</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="146">
@@ -5105,7 +5159,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5128,7 +5182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5152,7 +5206,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5326,7 @@
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>6 on salary: $46,500 a month incl. on-costs</t>
+          <t>6 employed full time: $60,192 in September incl. on-costs (every available hour at $60)</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5338,7 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>$60/hour for consultant time</t>
+          <t>$60/hour = consultant salaries incl. on-costs ÷ available hours, worked out each month; time charged to clients + time not charged = salaries</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5350,7 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>20 in August (Ekka show holiday), 22 in September; 7.6 hours a day</t>
+          <t>20 in August (21 weekdays, less the Ekka People's Day holiday, Wed 12 Aug), 22 in September; 7.6 hours a day</t>
         </is>
       </c>
     </row>
@@ -5344,120 +5398,188 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>GST, BAS and payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
-        <is>
-          <t>excluded throughout, for simplicity</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>registered; 10%, accruals basis: GST on a sale is owed when it's invoiced, a credit on a bill is claimed when it's received. The P&amp;L excludes GST; invoices, bills, debtors, creditors and cash include it</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>BAS</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>quarterly, self-lodged: GST on sales − GST credits + PAYG withheld + PAYG instalment. July to September is due 28 October; October to December, 28 February</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>Pay runs</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>fortnightly on Thursdays: $33,205 gross (a 26th of the year's gross wages); net pay $25,236 and super $3,985 paid on the day; PAYG withheld (about 24% of gross, $7,969) goes with the BAS. Two months a year have three pay runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>12% of gross wages, paid with each pay run (Payday Super, from 1 July 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>Payroll tax</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>none: Queensland's threshold is $1.3 million of wages a year (rate 4.75% above it); this business pays about $967,000 including super</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Banking days</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>money only moves on banking days: a payment due on a weekend or Queensland public holiday moves to the next banking day</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Checks (all passed)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>✓ Every subtotal and total adds up</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>✓ Balance sheet balances: assets = liabilities + equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>✓ Cash flow ends at the cash in the bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>✓ Profit ties to the movement in retained earnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>✓ Every engagement's revenue adds up to the P&amp;L</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>✓ Work in progress equals unbilled project time; debtors equal unpaid invoices</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Print check (done before this file was saved)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>✓ The fourth sheet: 1 page, 100% scale, no block split</t>
+          <t>✓ Balance sheet balances: assets = liabilities + equity</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>✓ Profit and loss: 1 page, 100% scale, no block split</t>
+          <t>✓ Cash flow ends at the cash in the bank</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>✓ Balance sheet: 1 page, 100% scale, no block split</t>
+          <t>✓ Profit ties to the movement in retained earnings</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>✓ Cash flow: 1 page, 100% scale, no block split</t>
+          <t>✓ Every engagement's revenue adds up to the P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>✓ Work in progress equals unbilled project time; debtors equal unpaid invoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Print check (done before this file was saved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>✓ The fourth sheet: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>✓ Profit and loss: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>✓ Balance sheet: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>✓ Cash flow: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>✓ Engagements: 1 page, 92% scale, no block split</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>✓ Workings: 7 pages, 100% scale, no block split</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>✓ Assumptions: 2 pages, 100% scale, no block split</t>
         </is>
@@ -5469,14 +5591,14 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="26" min="0" max="16383" man="1"/>
+    <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>